--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_pet/sub-0004_ses-01_pet_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_pet/sub-0004_ses-01_pet_pdf.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -222,7 +223,7 @@
         <v>0.083073727933541022</v>
       </c>
       <c r="O1" s="0">
-        <v>0.039549139806209221</v>
+        <v>0.039549139806209222</v>
       </c>
       <c r="P1" s="0">
         <v>0.068247739293635909</v>
@@ -441,7 +442,7 @@
         <v>0.033277870216306162</v>
       </c>
       <c r="CJ1" s="0">
-        <v>0.094876660341555979</v>
+        <v>0.09487666034155598</v>
       </c>
       <c r="CK1" s="0">
         <v>0.048247481197672776</v>
@@ -973,7 +974,7 @@
         <v>0</v>
       </c>
       <c r="X3" s="0">
-        <v>0.037900322152738294</v>
+        <v>0.037900322152738295</v>
       </c>
       <c r="Y3" s="0">
         <v>0</v>
@@ -1102,7 +1103,7 @@
         <v>0</v>
       </c>
       <c r="BO3" s="0">
-        <v>0.18011932905549929</v>
+        <v>0.1801193290554993</v>
       </c>
       <c r="BP3" s="0">
         <v>0</v>
@@ -1329,7 +1330,7 @@
         <v>0.037181632273656819</v>
       </c>
       <c r="V4" s="0">
-        <v>0.35232843137254904</v>
+        <v>0.35232843137254905</v>
       </c>
       <c r="W4" s="0">
         <v>0</v>
@@ -1670,7 +1671,7 @@
         <v>0.06230529595015577</v>
       </c>
       <c r="O5" s="0">
-        <v>0.039549139806209221</v>
+        <v>0.039549139806209222</v>
       </c>
       <c r="P5" s="0">
         <v>0.073935050901438898</v>
@@ -1838,7 +1839,7 @@
         <v>0.19375151368370067</v>
       </c>
       <c r="BS5" s="0">
-        <v>0.0080778706732905214</v>
+        <v>0.0080778706732905215</v>
       </c>
       <c r="BT5" s="0">
         <v>0.050877639277537523</v>
@@ -2203,7 +2204,7 @@
         <v>0.016155741346581043</v>
       </c>
       <c r="BT6" s="0">
-        <v>0.046637836004409398</v>
+        <v>0.046637836004409399</v>
       </c>
       <c r="BU6" s="0">
         <v>0.13470106724691741</v>
@@ -2269,7 +2270,7 @@
         <v>0</v>
       </c>
       <c r="CP6" s="0">
-        <v>0.0039972818483431267</v>
+        <v>0.0039972818483431268</v>
       </c>
       <c r="CQ6" s="0">
         <v>0</v>
@@ -2415,13 +2416,13 @@
         <v>0.037181632273656819</v>
       </c>
       <c r="V7" s="0">
-        <v>0.35232843137254904</v>
+        <v>0.35232843137254905</v>
       </c>
       <c r="W7" s="0">
         <v>0</v>
       </c>
       <c r="X7" s="0">
-        <v>0.037900322152738294</v>
+        <v>0.037900322152738295</v>
       </c>
       <c r="Y7" s="0">
         <v>0.052410901467505246</v>
@@ -3139,7 +3140,7 @@
         <v>0.1673173452314555</v>
       </c>
       <c r="V9" s="0">
-        <v>0.49019607843137208</v>
+        <v>0.49019607843137209</v>
       </c>
       <c r="W9" s="0">
         <v>0.017094017094017078</v>
@@ -3298,7 +3299,7 @@
         <v>0.049140049140049095</v>
       </c>
       <c r="BW9" s="0">
-        <v>0.04385964912280698</v>
+        <v>0.043859649122806981</v>
       </c>
       <c r="BX9" s="0">
         <v>0.15425606506801276</v>
@@ -3316,7 +3317,7 @@
         <v>0.26246719160104964</v>
       </c>
       <c r="CC9" s="0">
-        <v>0.32495938007749003</v>
+        <v>0.32495938007749004</v>
       </c>
       <c r="CD9" s="0">
         <v>0.064102564102564055</v>
@@ -3687,7 +3688,7 @@
         <v>0.063492063492063558</v>
       </c>
       <c r="CF10" s="0">
-        <v>0.40299366724237234</v>
+        <v>0.40299366724237235</v>
       </c>
       <c r="CG10" s="0">
         <v>0.053182059918454226</v>
@@ -3986,7 +3987,7 @@
         <v>0.040538050488299206</v>
       </c>
       <c r="BK11" s="0">
-        <v>0.068686036128854946</v>
+        <v>0.068686036128854947</v>
       </c>
       <c r="BL11" s="0">
         <v>0.15921538657495846</v>
@@ -4001,7 +4002,7 @@
         <v>0.54035798716649741</v>
       </c>
       <c r="BP11" s="0">
-        <v>0.02204585537918869</v>
+        <v>0.022045855379188691</v>
       </c>
       <c r="BQ11" s="0">
         <v>0.33500837520937993</v>
@@ -4234,7 +4235,7 @@
         <v>0.20845177184006086</v>
       </c>
       <c r="Y12" s="0">
-        <v>0.078616352201257927</v>
+        <v>0.078616352201257928</v>
       </c>
       <c r="Z12" s="0">
         <v>0.091512239762068265</v>
@@ -4270,7 +4271,7 @@
         <v>0.14447884416924681</v>
       </c>
       <c r="AK12" s="0">
-        <v>0.62402496099844051</v>
+        <v>0.62402496099844052</v>
       </c>
       <c r="AL12" s="0">
         <v>0.064487005868317598</v>
@@ -4330,7 +4331,7 @@
         <v>0.075368276807125795</v>
       </c>
       <c r="BE12" s="0">
-        <v>0.04688232536333807</v>
+        <v>0.046882325363338071</v>
       </c>
       <c r="BF12" s="0">
         <v>0.55532417048452087</v>
@@ -4375,7 +4376,7 @@
         <v>0.060584030049678966</v>
       </c>
       <c r="BT12" s="0">
-        <v>0.31798524548460982</v>
+        <v>0.31798524548460983</v>
       </c>
       <c r="BU12" s="0">
         <v>0.25904051393637989</v>
@@ -4429,7 +4430,7 @@
         <v>0.25826592876401333</v>
       </c>
       <c r="CL12" s="0">
-        <v>0.27156751294682357</v>
+        <v>0.27156751294682358</v>
       </c>
       <c r="CM12" s="0">
         <v>0.29811812930873888</v>
@@ -4533,7 +4534,7 @@
         <v>0.41243187509206036</v>
       </c>
       <c r="D13" s="0">
-        <v>0.25134551812692923</v>
+        <v>0.25134551812692924</v>
       </c>
       <c r="E13" s="0">
         <v>0.34576207831043798</v>
@@ -4551,13 +4552,13 @@
         <v>0.20487264673311165</v>
       </c>
       <c r="J13" s="0">
-        <v>0.31971353667114238</v>
+        <v>0.31971353667114239</v>
       </c>
       <c r="K13" s="0">
         <v>0.19004180919802341</v>
       </c>
       <c r="L13" s="0">
-        <v>0.23086485526549438</v>
+        <v>0.23086485526549439</v>
       </c>
       <c r="M13" s="0">
         <v>0.36036036036036007</v>
@@ -4728,10 +4729,10 @@
         <v>0.07348618459729564</v>
       </c>
       <c r="BQ13" s="0">
-        <v>0.40679588418281853</v>
+        <v>0.40679588418281854</v>
       </c>
       <c r="BR13" s="0">
-        <v>0.69427625736659337</v>
+        <v>0.69427625736659338</v>
       </c>
       <c r="BS13" s="0">
         <v>0.056545094713033595</v>
@@ -4916,7 +4917,7 @@
         <v>0.409233326939063</v>
       </c>
       <c r="K14" s="0">
-        <v>0.26605853287723324</v>
+        <v>0.26605853287723325</v>
       </c>
       <c r="L14" s="0">
         <v>0.28414136032676285</v>
@@ -4934,7 +4935,7 @@
         <v>0.35261331968378579</v>
       </c>
       <c r="Q14" s="0">
-        <v>0.41152263374485631</v>
+        <v>0.41152263374485632</v>
       </c>
       <c r="R14" s="0">
         <v>0.32139577594123081</v>
@@ -4979,7 +4980,7 @@
         <v>1.0928961748633892</v>
       </c>
       <c r="AF14" s="0">
-        <v>0.28070175438596517</v>
+        <v>0.28070175438596518</v>
       </c>
       <c r="AG14" s="0">
         <v>0.090538705296514352</v>
@@ -5069,7 +5070,7 @@
         <v>0.2976510668818364</v>
       </c>
       <c r="BJ14" s="0">
-        <v>0.088446655610834798</v>
+        <v>0.088446655610834799</v>
       </c>
       <c r="BK14" s="0">
         <v>0.13737207225771014</v>
@@ -5156,7 +5157,7 @@
         <v>0.38840469874952671</v>
       </c>
       <c r="CM14" s="0">
-        <v>0.37264766163592355</v>
+        <v>0.37264766163592356</v>
       </c>
       <c r="CN14" s="0">
         <v>0.035893754486719345</v>
@@ -5326,7 +5327,7 @@
         <v>0.2059025394646532</v>
       </c>
       <c r="AA15" s="0">
-        <v>0.23453532688361164</v>
+        <v>0.23453532688361165</v>
       </c>
       <c r="AB15" s="0">
         <v>0.24524831391784158</v>
@@ -5431,7 +5432,7 @@
         <v>0.28689259458490202</v>
       </c>
       <c r="BJ15" s="0">
-        <v>0.081076100976598411</v>
+        <v>0.081076100976598412</v>
       </c>
       <c r="BK15" s="0">
         <v>0.26787554090253429</v>
@@ -5446,7 +5447,7 @@
         <v>0.1448825416537306</v>
       </c>
       <c r="BO15" s="0">
-        <v>1.1032308904649319</v>
+        <v>1.103230890464932</v>
       </c>
       <c r="BP15" s="0">
         <v>0.12492651381540258</v>
@@ -5610,7 +5611,7 @@
     </row>
     <row r="16">
       <c r="A16" s="0">
-        <v>0.46290705631365014</v>
+        <v>0.46290705631365015</v>
       </c>
       <c r="B16" s="0">
         <v>0.48503094162903543</v>
@@ -5652,7 +5653,7 @@
         <v>0.57113187954309497</v>
       </c>
       <c r="O16" s="0">
-        <v>0.52073034078175517</v>
+        <v>0.52073034078175518</v>
       </c>
       <c r="P16" s="0">
         <v>0.60854234203492064</v>
@@ -5688,7 +5689,7 @@
         <v>0.25165865934568771</v>
       </c>
       <c r="AA16" s="0">
-        <v>0.20521841102316057</v>
+        <v>0.20521841102316058</v>
       </c>
       <c r="AB16" s="0">
         <v>0.18393623543838156</v>
@@ -5742,7 +5743,7 @@
         <v>0.049844236760124658</v>
       </c>
       <c r="AS16" s="0">
-        <v>0.33068783068783097</v>
+        <v>0.33068783068783098</v>
       </c>
       <c r="AT16" s="0">
         <v>0.16694490818030067</v>
@@ -5781,7 +5782,7 @@
         <v>0.20315674324113162</v>
       </c>
       <c r="BF16" s="0">
-        <v>1.1106483409690417</v>
+        <v>1.1106483409690418</v>
       </c>
       <c r="BG16" s="0">
         <v>0.036968576709796704</v>
@@ -5984,7 +5985,7 @@
         <v>0.48083490424282116</v>
       </c>
       <c r="E17" s="0">
-        <v>0.60430489362364836</v>
+        <v>0.60430489362364837</v>
       </c>
       <c r="F17" s="0">
         <v>0.48779088117987968</v>
@@ -6008,7 +6009,7 @@
         <v>0.55052388563310195</v>
       </c>
       <c r="M17" s="0">
-        <v>0.49896049896049854</v>
+        <v>0.49896049896049855</v>
       </c>
       <c r="N17" s="0">
         <v>0.6749740394600201</v>
@@ -6044,7 +6045,7 @@
         <v>0.49270418798559745</v>
       </c>
       <c r="Y17" s="0">
-        <v>0.44549266247379415</v>
+        <v>0.44549266247379416</v>
       </c>
       <c r="Z17" s="0">
         <v>0.16014641958361917</v>
@@ -6230,7 +6231,7 @@
         <v>0.16783710966830073</v>
       </c>
       <c r="CI17" s="0">
-        <v>0.44370493621741502</v>
+        <v>0.44370493621741503</v>
       </c>
       <c r="CJ17" s="0">
         <v>0.75901328273244717</v>
@@ -6493,7 +6494,7 @@
         <v>0.56621579112928544</v>
       </c>
       <c r="BB18" s="0">
-        <v>0.24640252316183694</v>
+        <v>0.24640252316183695</v>
       </c>
       <c r="BC18" s="0">
         <v>0.13966480446927362</v>
@@ -6532,7 +6533,7 @@
         <v>0.22767256545586237</v>
       </c>
       <c r="BO18" s="0">
-        <v>1.3283800517843058</v>
+        <v>1.3283800517843059</v>
       </c>
       <c r="BP18" s="0">
         <v>0.22780717225161648</v>
@@ -6601,7 +6602,7 @@
         <v>0.6924932595430674</v>
       </c>
       <c r="CL18" s="0">
-        <v>0.6789187823670576</v>
+        <v>0.67891878236705761</v>
       </c>
       <c r="CM18" s="0">
         <v>0.85708962176262271</v>
@@ -6613,7 +6614,7 @@
         <v>0.17632019747862102</v>
       </c>
       <c r="CP18" s="0">
-        <v>0.12791301914697994</v>
+        <v>0.12791301914697995</v>
       </c>
       <c r="CQ18" s="0">
         <v>0</v>
@@ -6696,7 +6697,7 @@
     </row>
     <row r="19">
       <c r="A19" s="0">
-        <v>0.73662601135128813</v>
+        <v>0.73662601135128814</v>
       </c>
       <c r="B19" s="0">
         <v>0.70663990633885465</v>
@@ -6708,7 +6709,7 @@
         <v>0.62836379531732556</v>
       </c>
       <c r="E19" s="0">
-        <v>0.76005357754727187</v>
+        <v>0.76005357754727188</v>
       </c>
       <c r="F19" s="0">
         <v>0.60256520616338294</v>
@@ -6732,7 +6733,7 @@
         <v>0.92345942106198087</v>
       </c>
       <c r="M19" s="0">
-        <v>0.98406098406098685</v>
+        <v>0.98406098406098686</v>
       </c>
       <c r="N19" s="0">
         <v>0.83073727933541253</v>
@@ -6771,7 +6772,7 @@
         <v>0.83857442348008626</v>
       </c>
       <c r="Z19" s="0">
-        <v>0.45756119881034218</v>
+        <v>0.45756119881034219</v>
       </c>
       <c r="AA19" s="0">
         <v>0.41043682204632187</v>
@@ -6816,7 +6817,7 @@
         <v>0.30421555845284742</v>
       </c>
       <c r="AO19" s="0">
-        <v>1.3782771535580562</v>
+        <v>1.3782771535580563</v>
       </c>
       <c r="AP19" s="0">
         <v>0.30905077262693248</v>
@@ -6825,16 +6826,16 @@
         <v>0.52932761087267677</v>
       </c>
       <c r="AR19" s="0">
-        <v>0.14953271028037426</v>
+        <v>0.14953271028037427</v>
       </c>
       <c r="AS19" s="0">
-        <v>0.72751322751322955</v>
+        <v>0.72751322751322956</v>
       </c>
       <c r="AT19" s="0">
         <v>0.22259321090706796</v>
       </c>
       <c r="AU19" s="0">
-        <v>0.64910979228486831</v>
+        <v>0.64910979228486832</v>
       </c>
       <c r="AV19" s="0">
         <v>0.08942544153811785</v>
@@ -7073,7 +7074,7 @@
         <v>0.8784225773292208</v>
       </c>
       <c r="F20" s="0">
-        <v>0.77185733551404478</v>
+        <v>0.77185733551404479</v>
       </c>
       <c r="G20" s="0">
         <v>0.76121794871794801</v>
@@ -7187,7 +7188,7 @@
         <v>0.61516452074391925</v>
       </c>
       <c r="AR20" s="0">
-        <v>0.2367601246105917</v>
+        <v>0.23676012461059171</v>
       </c>
       <c r="AS20" s="0">
         <v>0.26455026455026431</v>
@@ -7205,7 +7206,7 @@
         <v>0.33189809831359857</v>
       </c>
       <c r="AX20" s="0">
-        <v>0.41527397954015965</v>
+        <v>0.41527397954015966</v>
       </c>
       <c r="AY20" s="0">
         <v>1.1729019211324558</v>
@@ -7226,7 +7227,7 @@
         <v>0.65775950668036942</v>
       </c>
       <c r="BE20" s="0">
-        <v>0.48445069542115909</v>
+        <v>0.4844506954211591</v>
       </c>
       <c r="BF20" s="0">
         <v>1.5271414688324296</v>
@@ -7256,7 +7257,7 @@
         <v>0.27941633033219471</v>
       </c>
       <c r="BO20" s="0">
-        <v>1.879995497016772</v>
+        <v>1.8799954970167721</v>
       </c>
       <c r="BP20" s="0">
         <v>0.35273368606701905</v>
@@ -7337,7 +7338,7 @@
         <v>0.29974433571365572</v>
       </c>
       <c r="CP20" s="0">
-        <v>0.17588040132709742</v>
+        <v>0.17588040132709743</v>
       </c>
       <c r="CQ20" s="0">
         <v>0</v>
@@ -7531,7 +7532,7 @@
         <v>1.2554787905801936</v>
       </c>
       <c r="AL21" s="0">
-        <v>0.54169084929386679</v>
+        <v>0.5416908492938668</v>
       </c>
       <c r="AM21" s="0">
         <v>0.98856966326845763</v>
@@ -7540,7 +7541,7 @@
         <v>0.13037809647979129</v>
       </c>
       <c r="AO21" s="0">
-        <v>1.4232209737827703</v>
+        <v>1.4232209737827704</v>
       </c>
       <c r="AP21" s="0">
         <v>0.44150110375275897</v>
@@ -7561,7 +7562,7 @@
         <v>0.81602373887240276</v>
       </c>
       <c r="AV21" s="0">
-        <v>0.17885088307623503</v>
+        <v>0.17885088307623504</v>
       </c>
       <c r="AW21" s="0">
         <v>0.66379619662719713</v>
@@ -7612,7 +7613,7 @@
         <v>0.84065724111578077</v>
       </c>
       <c r="BM21" s="0">
-        <v>0.35343878556115615</v>
+        <v>0.35343878556115616</v>
       </c>
       <c r="BN21" s="0">
         <v>0.43464762496119175</v>
@@ -7657,7 +7658,7 @@
         <v>1.2030075187969915</v>
       </c>
       <c r="CB21" s="0">
-        <v>1.5223097112860879</v>
+        <v>1.522309711286088</v>
       </c>
       <c r="CC21" s="0">
         <v>1.5373078365204336</v>
@@ -7851,7 +7852,7 @@
         <v>0.41025641025640991</v>
       </c>
       <c r="X22" s="0">
-        <v>0.83380708736024189</v>
+        <v>0.8338070873602419</v>
       </c>
       <c r="Y22" s="0">
         <v>1.0220125786163512</v>
@@ -7902,7 +7903,7 @@
         <v>0.34767492394611005</v>
       </c>
       <c r="AO22" s="0">
-        <v>1.4232209737827703</v>
+        <v>1.4232209737827704</v>
       </c>
       <c r="AP22" s="0">
         <v>0.48565121412803491</v>
@@ -7983,7 +7984,7 @@
         <v>1.429697174378024</v>
       </c>
       <c r="BP22" s="0">
-        <v>0.63932980599647204</v>
+        <v>0.63932980599647205</v>
       </c>
       <c r="BQ22" s="0">
         <v>1.3280689160086132</v>
@@ -8198,13 +8199,13 @@
         <v>0.78053259871441916</v>
       </c>
       <c r="S23" s="0">
-        <v>1.1516671310485775</v>
+        <v>1.1516671310485776</v>
       </c>
       <c r="T23" s="0">
         <v>1.181451888274264</v>
       </c>
       <c r="U23" s="0">
-        <v>1.2455846811675066</v>
+        <v>1.2455846811675067</v>
       </c>
       <c r="V23" s="0">
         <v>1.4093137254902002</v>
@@ -8279,7 +8280,7 @@
         <v>0.66137566137566317</v>
       </c>
       <c r="AT23" s="0">
-        <v>0.44518642181413592</v>
+        <v>0.44518642181413593</v>
       </c>
       <c r="AU23" s="0">
         <v>0.82220573689416654</v>
@@ -8396,7 +8397,7 @@
         <v>1.2665515256188866</v>
       </c>
       <c r="CG23" s="0">
-        <v>0.7504579566270777</v>
+        <v>0.75045795662707771</v>
       </c>
       <c r="CH23" s="0">
         <v>0.59626341592686005</v>
@@ -8408,7 +8409,7 @@
         <v>1.3809825005270964</v>
       </c>
       <c r="CK23" s="0">
-        <v>1.1919965942954482</v>
+        <v>1.1919965942954483</v>
       </c>
       <c r="CL23" s="0">
         <v>1.2410003789314168</v>
@@ -8551,7 +8552,7 @@
         <v>1.1666996242831709</v>
       </c>
       <c r="P24" s="0">
-        <v>1.1886481260308241</v>
+        <v>1.1886481260308242</v>
       </c>
       <c r="Q24" s="0">
         <v>1.2860082304526737</v>
@@ -8569,7 +8570,7 @@
         <v>1.0782673359360466</v>
       </c>
       <c r="V24" s="0">
-        <v>1.4093137254901948</v>
+        <v>1.4093137254901949</v>
       </c>
       <c r="W24" s="0">
         <v>0.51282051282051244</v>
@@ -8590,7 +8591,7 @@
         <v>0.65399550378091087</v>
       </c>
       <c r="AC24" s="0">
-        <v>1.7021276595744665</v>
+        <v>1.7021276595744666</v>
       </c>
       <c r="AD24" s="0">
         <v>0.52343564120866004</v>
@@ -8662,7 +8663,7 @@
         <v>1.0559466469062606</v>
       </c>
       <c r="BA24" s="0">
-        <v>1.1743734927125919</v>
+        <v>1.174373492712592</v>
       </c>
       <c r="BB24" s="0">
         <v>0.64064656022077604</v>
@@ -8725,7 +8726,7 @@
         <v>1.2123096052222557</v>
       </c>
       <c r="BV24" s="0">
-        <v>0.85176085176085103</v>
+        <v>0.85176085176085104</v>
       </c>
       <c r="BW24" s="0">
         <v>1.1842105263157885</v>
@@ -8904,7 +8905,7 @@
         <v>1.349671461552121</v>
       </c>
       <c r="M25" s="0">
-        <v>1.2889812889812879</v>
+        <v>1.288981288981288</v>
       </c>
       <c r="N25" s="0">
         <v>1.5057113187954296</v>
@@ -9081,7 +9082,7 @@
         <v>0.72296942525950092</v>
       </c>
       <c r="BT25" s="0">
-        <v>1.3355380310353588</v>
+        <v>1.3355380310353589</v>
       </c>
       <c r="BU25" s="0">
         <v>1.4195420163713592</v>
@@ -9126,7 +9127,7 @@
         <v>0.79501788790247707</v>
       </c>
       <c r="CI25" s="0">
-        <v>1.3422074320576804</v>
+        <v>1.3422074320576805</v>
       </c>
       <c r="CJ25" s="0">
         <v>1.4758591608686471</v>
@@ -9278,7 +9279,7 @@
         <v>1.3877040323039287</v>
       </c>
       <c r="Q26" s="0">
-        <v>1.5946502057613154</v>
+        <v>1.5946502057613155</v>
       </c>
       <c r="R26" s="0">
         <v>1.4233241505968766</v>
@@ -9365,7 +9366,7 @@
         <v>1.3227513227513215</v>
       </c>
       <c r="AT26" s="0">
-        <v>0.44518642181413431</v>
+        <v>0.44518642181413432</v>
       </c>
       <c r="AU26" s="0">
         <v>1.2982195845697317</v>
@@ -9392,7 +9393,7 @@
         <v>0.84762467967671917</v>
       </c>
       <c r="BC26" s="0">
-        <v>0.52480108346030085</v>
+        <v>0.52480108346030086</v>
       </c>
       <c r="BD26" s="0">
         <v>1.1442274751627259</v>
@@ -9476,7 +9477,7 @@
         <v>0.99999999999999911</v>
       </c>
       <c r="CE26" s="0">
-        <v>1.3333333333333321</v>
+        <v>1.3333333333333322</v>
       </c>
       <c r="CF26" s="0">
         <v>1.6119746689694863</v>
@@ -9509,7 +9510,7 @@
         <v>0.60389667636427691</v>
       </c>
       <c r="CP26" s="0">
-        <v>0.57161130431306661</v>
+        <v>0.57161130431306662</v>
       </c>
       <c r="CQ26" s="0">
         <v>0</v>
@@ -9542,7 +9543,7 @@
         <v>0.38064165307232162</v>
       </c>
       <c r="DA26" s="0">
-        <v>2.8338136407300651</v>
+        <v>2.8338136407300652</v>
       </c>
       <c r="DB26" s="0">
         <v>0.28735632183908022</v>
@@ -9554,7 +9555,7 @@
         <v>0.26715239829993903</v>
       </c>
       <c r="DE26" s="0">
-        <v>0.096665055582406872</v>
+        <v>0.096665055582406873</v>
       </c>
       <c r="DF26" s="0">
         <v>4.0558963871847267</v>
@@ -9563,7 +9564,7 @@
         <v>1.2195121951219501</v>
       </c>
       <c r="DH26" s="0">
-        <v>0.89126559714794928</v>
+        <v>0.89126559714794929</v>
       </c>
       <c r="DI26" s="0">
         <v>0</v>
@@ -9646,7 +9647,7 @@
         <v>1.2855831037649208</v>
       </c>
       <c r="S27" s="0">
-        <v>1.5742546670381707</v>
+        <v>1.5742546670381708</v>
       </c>
       <c r="T27" s="0">
         <v>1.502424366591544</v>
@@ -9691,7 +9692,7 @@
         <v>0.71676475026407049</v>
       </c>
       <c r="AH27" s="0">
-        <v>1.2369172216936239</v>
+        <v>1.236917221693624</v>
       </c>
       <c r="AI27" s="0">
         <v>1.3276578493969786</v>
@@ -9745,10 +9746,10 @@
         <v>1.3414223120997628</v>
       </c>
       <c r="AZ27" s="0">
-        <v>1.2659009509694938</v>
+        <v>1.2659009509694939</v>
       </c>
       <c r="BA27" s="0">
-        <v>1.3840830449826977</v>
+        <v>1.3840830449826978</v>
       </c>
       <c r="BB27" s="0">
         <v>0.94618568894145394</v>
@@ -9898,7 +9899,7 @@
         <v>0</v>
       </c>
       <c r="CY27" s="0">
-        <v>0.38090607018396921</v>
+        <v>0.38090607018396922</v>
       </c>
       <c r="CZ27" s="0">
         <v>0.52046919909888867</v>
@@ -9913,7 +9914,7 @@
         <v>0</v>
       </c>
       <c r="DD27" s="0">
-        <v>0.56466302367941656</v>
+        <v>0.56466302367941657</v>
       </c>
       <c r="DE27" s="0">
         <v>0.14499758337361032</v>
@@ -9954,7 +9955,7 @@
     </row>
     <row r="28">
       <c r="A28" s="0">
-        <v>1.3323672664332042</v>
+        <v>1.3323672664332043</v>
       </c>
       <c r="B28" s="0">
         <v>1.4132798126777093</v>
@@ -10083,7 +10084,7 @@
         <v>1.3018597997138805</v>
       </c>
       <c r="AR28" s="0">
-        <v>0.84735202492212069</v>
+        <v>0.8473520249221207</v>
       </c>
       <c r="AS28" s="0">
         <v>0.92592592592592848</v>
@@ -10131,7 +10132,7 @@
         <v>0.56685150955021724</v>
       </c>
       <c r="BH28" s="0">
-        <v>0.56894243641231756</v>
+        <v>0.56894243641231757</v>
       </c>
       <c r="BI28" s="0">
         <v>1.4165321857629589</v>
@@ -10233,7 +10234,7 @@
         <v>0.96976108613241918</v>
       </c>
       <c r="CP28" s="0">
-        <v>0.76747811488188244</v>
+        <v>0.76747811488188245</v>
       </c>
       <c r="CQ28" s="0">
         <v>0.021673168617251902</v>
@@ -10269,13 +10270,13 @@
         <v>4.1306436119116352</v>
       </c>
       <c r="DB28" s="0">
-        <v>1.123301985370954</v>
+        <v>1.1233019853709541</v>
       </c>
       <c r="DC28" s="0">
         <v>0.029935638377488482</v>
       </c>
       <c r="DD28" s="0">
-        <v>0.9896782027929597</v>
+        <v>0.98967820279295971</v>
       </c>
       <c r="DE28" s="0">
         <v>0.41888190752376464</v>
@@ -10319,7 +10320,7 @@
         <v>1.5296059252103194</v>
       </c>
       <c r="B29" s="0">
-        <v>1.5596253554106025</v>
+        <v>1.5596253554106026</v>
       </c>
       <c r="C29" s="0">
         <v>1.3993224333480618</v>
@@ -10343,7 +10344,7 @@
         <v>1.4507198228128448</v>
       </c>
       <c r="J29" s="0">
-        <v>1.3875567491527578</v>
+        <v>1.3875567491527579</v>
       </c>
       <c r="K29" s="0">
         <v>1.1972633979475475</v>
@@ -10382,7 +10383,7 @@
         <v>1.0416666666666659</v>
       </c>
       <c r="W29" s="0">
-        <v>0.94017094017093938</v>
+        <v>0.94017094017093939</v>
       </c>
       <c r="X29" s="0">
         <v>1.4970627250331614</v>
@@ -10598,7 +10599,7 @@
         <v>0.90338569772554578</v>
       </c>
       <c r="CQ29" s="0">
-        <v>0.032509752925877738</v>
+        <v>0.032509752925877739</v>
       </c>
       <c r="CR29" s="0">
         <v>4.0694577607329245</v>
@@ -10631,7 +10632,7 @@
         <v>4.6109510086455296</v>
       </c>
       <c r="DB29" s="0">
-        <v>1.6196447230929973</v>
+        <v>1.6196447230929974</v>
       </c>
       <c r="DC29" s="0">
         <v>0.074839095943720943</v>
@@ -10714,7 +10715,7 @@
         <v>1.6693304919197285</v>
       </c>
       <c r="M30" s="0">
-        <v>1.455301455301454</v>
+        <v>1.4553014553014541</v>
       </c>
       <c r="N30" s="0">
         <v>1.391484942886811</v>
@@ -10744,7 +10745,7 @@
         <v>0.87316176470588158</v>
       </c>
       <c r="W30" s="0">
-        <v>1.282051282051281</v>
+        <v>1.2820512820512811</v>
       </c>
       <c r="X30" s="0">
         <v>1.5349630471858997</v>
@@ -10849,7 +10850,7 @@
         <v>1.3127051101734635</v>
       </c>
       <c r="BF30" s="0">
-        <v>1.0134666111342487</v>
+        <v>1.0134666111342488</v>
       </c>
       <c r="BG30" s="0">
         <v>0.75169439309919828</v>
@@ -10888,7 +10889,7 @@
         <v>1.2028739807863074</v>
       </c>
       <c r="BS30" s="0">
-        <v>1.2520699543600295</v>
+        <v>1.2520699543600296</v>
       </c>
       <c r="BT30" s="0">
         <v>1.3100992113965901</v>
@@ -10900,7 +10901,7 @@
         <v>1.3595413595413584</v>
       </c>
       <c r="BW30" s="0">
-        <v>1.6520467836257295</v>
+        <v>1.6520467836257296</v>
       </c>
       <c r="BX30" s="0">
         <v>1.1639321273313692</v>
@@ -10921,7 +10922,7 @@
         <v>1.0623672040994865</v>
       </c>
       <c r="CD30" s="0">
-        <v>1.3333333333333321</v>
+        <v>1.3333333333333322</v>
       </c>
       <c r="CE30" s="0">
         <v>1.5238095238095224</v>
@@ -10936,7 +10937,7 @@
         <v>1.1925268318537157</v>
       </c>
       <c r="CI30" s="0">
-        <v>1.3422074320576804</v>
+        <v>1.3422074320576805</v>
       </c>
       <c r="CJ30" s="0">
         <v>1.4126080539742767</v>
@@ -11026,13 +11027,13 @@
         <v>1.3489991296779797</v>
       </c>
       <c r="DM30" s="0">
-        <v>0.49857549857549815</v>
+        <v>0.49857549857549816</v>
       </c>
       <c r="DN30" s="0">
         <v>1.3671874999999989</v>
       </c>
       <c r="DO30" s="0">
-        <v>1.7799352750809045</v>
+        <v>1.7799352750809046</v>
       </c>
       <c r="DP30" s="0">
         <v>4.3427230046948315</v>
@@ -11046,7 +11047,7 @@
         <v>1.4425489212242837</v>
       </c>
       <c r="C31" s="0">
-        <v>1.4317277949624378</v>
+        <v>1.4317277949624379</v>
       </c>
       <c r="D31" s="0">
         <v>1.4971450427560569</v>
@@ -11106,7 +11107,7 @@
         <v>0.765931372549019</v>
       </c>
       <c r="W31" s="0">
-        <v>1.282051282051281</v>
+        <v>1.2820512820512811</v>
       </c>
       <c r="X31" s="0">
         <v>1.572863369338638</v>
@@ -11166,7 +11167,7 @@
         <v>1.2509197939661503</v>
       </c>
       <c r="AQ31" s="0">
-        <v>1.5164520743919871</v>
+        <v>1.5164520743919872</v>
       </c>
       <c r="AR31" s="0">
         <v>1.3208722741433012</v>
@@ -11211,7 +11212,7 @@
         <v>1.3439599937490221</v>
       </c>
       <c r="BF31" s="0">
-        <v>0.93016798556157076</v>
+        <v>0.93016798556157077</v>
       </c>
       <c r="BG31" s="0">
         <v>0.75169439309919828</v>
@@ -11226,7 +11227,7 @@
         <v>1.4519992629445353</v>
       </c>
       <c r="BK31" s="0">
-        <v>1.4492753623188392</v>
+        <v>1.4492753623188393</v>
       </c>
       <c r="BL31" s="0">
         <v>1.2482486307476746</v>
@@ -11301,7 +11302,7 @@
         <v>1.3976705490848573</v>
       </c>
       <c r="CJ31" s="0">
-        <v>1.3388150959308442</v>
+        <v>1.3388150959308443</v>
       </c>
       <c r="CK31" s="0">
         <v>1.3339009507591872</v>
@@ -11429,7 +11430,7 @@
         <v>1.4119601328903695</v>
       </c>
       <c r="J32" s="0">
-        <v>1.3683739369524945</v>
+        <v>1.3683739369524946</v>
       </c>
       <c r="K32" s="0">
         <v>1.5203344735841928</v>
@@ -11525,7 +11526,7 @@
         <v>0.97378277153558335</v>
       </c>
       <c r="AP32" s="0">
-        <v>1.3686534216335577</v>
+        <v>1.3686534216335578</v>
       </c>
       <c r="AQ32" s="0">
         <v>1.3161659513590882</v>
@@ -11675,7 +11676,7 @@
         <v>1.3228991988075312</v>
       </c>
       <c r="CN32" s="0">
-        <v>1.172529313232834</v>
+        <v>1.1725293132328341</v>
       </c>
       <c r="CO32" s="0">
         <v>1.2739134267830416</v>
@@ -11803,7 +11804,7 @@
         <v>1.2474012474012464</v>
       </c>
       <c r="N33" s="0">
-        <v>1.3187954309449625</v>
+        <v>1.3187954309449626</v>
       </c>
       <c r="O33" s="0">
         <v>1.2985300903038681</v>
@@ -11875,7 +11876,7 @@
         <v>0.91375083574771476</v>
       </c>
       <c r="AL33" s="0">
-        <v>1.4509576320371433</v>
+        <v>1.4509576320371434</v>
       </c>
       <c r="AM33" s="0">
         <v>0.95767686129131824</v>
@@ -11908,7 +11909,7 @@
         <v>1.1103658990982925</v>
       </c>
       <c r="AW33" s="0">
-        <v>1.6864011481880143</v>
+        <v>1.6864011481880144</v>
       </c>
       <c r="AX33" s="0">
         <v>1.1141497012053063</v>
@@ -11971,13 +11972,13 @@
         <v>1.1127063890882978</v>
       </c>
       <c r="BR33" s="0">
-        <v>0.80729797368208533</v>
+        <v>0.80729797368208534</v>
       </c>
       <c r="BS33" s="0">
         <v>1.3086150490730633</v>
       </c>
       <c r="BT33" s="0">
-        <v>1.2465021622996681</v>
+        <v>1.2465021622996682</v>
       </c>
       <c r="BU33" s="0">
         <v>1.2641177080095316</v>
@@ -12300,7 +12301,7 @@
         <v>0.72192142162987571</v>
       </c>
       <c r="BG34" s="0">
-        <v>1.2076401725200236</v>
+        <v>1.2076401725200237</v>
       </c>
       <c r="BH34" s="0">
         <v>1.0542168674698784</v>
@@ -12575,7 +12576,7 @@
         <v>0.28368794326241109</v>
       </c>
       <c r="AD35" s="0">
-        <v>1.0706638115631681</v>
+        <v>1.0706638115631682</v>
       </c>
       <c r="AE35" s="0">
         <v>1.7076502732240422</v>
@@ -12587,7 +12588,7 @@
         <v>1.5617926663648696</v>
       </c>
       <c r="AH35" s="0">
-        <v>1.2607040913415783</v>
+        <v>1.2607040913415784</v>
       </c>
       <c r="AI35" s="0">
         <v>1.1148272017837224</v>
@@ -12605,7 +12606,7 @@
         <v>0.89589125733703967</v>
       </c>
       <c r="AN35" s="0">
-        <v>1.999130812690133</v>
+        <v>1.9991308126901331</v>
       </c>
       <c r="AO35" s="0">
         <v>0.62921348314606684</v>
@@ -12797,7 +12798,7 @@
         <v>4.1656536186076627</v>
       </c>
       <c r="CZ35" s="0">
-        <v>3.4102384836479422</v>
+        <v>3.4102384836479423</v>
       </c>
       <c r="DA35" s="0">
         <v>0.5523535062439956</v>
@@ -12862,7 +12863,7 @@
         <v>1.2731196896429244</v>
       </c>
       <c r="E36" s="0">
-        <v>1.0248263402174242</v>
+        <v>1.0248263402174243</v>
       </c>
       <c r="F36" s="0">
         <v>1.0960948035924354</v>
@@ -12943,7 +12944,7 @@
         <v>0.54644808743169349</v>
       </c>
       <c r="AF36" s="0">
-        <v>1.3333333333333321</v>
+        <v>1.3333333333333322</v>
       </c>
       <c r="AG36" s="0">
         <v>1.448619284744227</v>
@@ -12979,7 +12980,7 @@
         <v>1.173104434907009</v>
       </c>
       <c r="AR36" s="0">
-        <v>1.3333333333333321</v>
+        <v>1.3333333333333322</v>
       </c>
       <c r="AS36" s="0">
         <v>1.1243386243386233</v>
@@ -13138,7 +13139,7 @@
         <v>0.59656972408650211</v>
       </c>
       <c r="CS36" s="0">
-        <v>2.565236620964173</v>
+        <v>2.5652366209641731</v>
       </c>
       <c r="CT36" s="0">
         <v>4.2918168468829219</v>
@@ -13168,7 +13169,7 @@
         <v>3.0825496342737693</v>
       </c>
       <c r="DC36" s="0">
-        <v>3.5847926957042326</v>
+        <v>3.5847926957042327</v>
       </c>
       <c r="DD36" s="0">
         <v>3.0297510625379451</v>
@@ -13183,7 +13184,7 @@
         <v>0.40650406504065006</v>
       </c>
       <c r="DH36" s="0">
-        <v>0.89126559714794928</v>
+        <v>0.89126559714794929</v>
       </c>
       <c r="DI36" s="0">
         <v>4.0498442367601211</v>
@@ -13224,7 +13225,7 @@
         <v>1.2130153266125716</v>
       </c>
       <c r="E37" s="0">
-        <v>1.0248263402174242</v>
+        <v>1.0248263402174243</v>
       </c>
       <c r="F37" s="0">
         <v>1.1391351754612484</v>
@@ -13254,7 +13255,7 @@
         <v>0.80996884735202423</v>
       </c>
       <c r="O37" s="0">
-        <v>0.98213697185419468</v>
+        <v>0.98213697185419469</v>
       </c>
       <c r="P37" s="0">
         <v>1.1545242563840064</v>
@@ -13275,7 +13276,7 @@
         <v>1.0596765197992182</v>
       </c>
       <c r="V37" s="0">
-        <v>0.29105392156862719</v>
+        <v>0.2910539215686272</v>
       </c>
       <c r="W37" s="0">
         <v>1.264957264957264</v>
@@ -13326,7 +13327,7 @@
         <v>1.251047913845359</v>
       </c>
       <c r="AM37" s="0">
-        <v>0.52517763361136804</v>
+        <v>0.52517763361136805</v>
       </c>
       <c r="AN37" s="0">
         <v>1.1734028683181215</v>
@@ -13482,7 +13483,7 @@
         <v>1.0073260073260064</v>
       </c>
       <c r="CM37" s="0">
-        <v>0.80119247251723424</v>
+        <v>0.80119247251723425</v>
       </c>
       <c r="CN37" s="0">
         <v>1.4836085187843968</v>
@@ -13518,7 +13519,7 @@
         <v>3.7232342601470081</v>
       </c>
       <c r="CY37" s="0">
-        <v>2.1233487316638286</v>
+        <v>2.1233487316638287</v>
       </c>
       <c r="CZ37" s="0">
         <v>2.159558766410314</v>
@@ -13604,7 +13605,7 @@
         <v>0.93356352707974266</v>
       </c>
       <c r="K38" s="0">
-        <v>1.0832383124287412</v>
+        <v>1.0832383124287413</v>
       </c>
       <c r="L38" s="0">
         <v>0.94121825608240717</v>
@@ -13700,7 +13701,7 @@
         <v>1.3539367181751376</v>
       </c>
       <c r="AQ38" s="0">
-        <v>1.2017167381974327</v>
+        <v>1.2017167381974328</v>
       </c>
       <c r="AR38" s="0">
         <v>1.5202492211838106</v>
@@ -13826,7 +13827,7 @@
         <v>0.57570523891767789</v>
       </c>
       <c r="CG38" s="0">
-        <v>1.0636411983690905</v>
+        <v>1.0636411983690906</v>
       </c>
       <c r="CH38" s="0">
         <v>1.38244777174154</v>
@@ -13862,7 +13863,7 @@
         <v>0.11718333865984949</v>
       </c>
       <c r="CS38" s="0">
-        <v>1.238390092879265</v>
+        <v>1.2383900928792651</v>
       </c>
       <c r="CT38" s="0">
         <v>3.3039647577092723</v>
@@ -13880,7 +13881,7 @@
         <v>4.0428251837648075</v>
       </c>
       <c r="CY38" s="0">
-        <v>1.6532944322878786</v>
+        <v>1.6532944322878787</v>
       </c>
       <c r="CZ38" s="0">
         <v>1.1652295502214014</v>
@@ -14029,7 +14030,7 @@
         <v>0.54644808743169349</v>
       </c>
       <c r="AF39" s="0">
-        <v>1.684210526315788</v>
+        <v>1.6842105263157881</v>
       </c>
       <c r="AG39" s="0">
         <v>1.6070620190131268</v>
@@ -14128,7 +14129,7 @@
         <v>0.95529231944975079</v>
       </c>
       <c r="BM39" s="0">
-        <v>1.4195492206964468</v>
+        <v>1.4195492206964469</v>
       </c>
       <c r="BN39" s="0">
         <v>1.6144054641415695</v>
@@ -14155,7 +14156,7 @@
         <v>0.76675992125168313</v>
       </c>
       <c r="BV39" s="0">
-        <v>1.3104013104013092</v>
+        <v>1.3104013104013093</v>
       </c>
       <c r="BW39" s="0">
         <v>0.89181286549707528</v>
@@ -14367,7 +14368,7 @@
         <v>1.1623931623931614</v>
       </c>
       <c r="X40" s="0">
-        <v>0.83380708736024189</v>
+        <v>0.8338070873602419</v>
       </c>
       <c r="Y40" s="0">
         <v>1.0220125786163512</v>
@@ -14469,7 +14470,7 @@
         <v>0.96890139084231819</v>
       </c>
       <c r="BF40" s="0">
-        <v>0.2637789809801469</v>
+        <v>0.26377898098014691</v>
       </c>
       <c r="BG40" s="0">
         <v>1.5033887861983966</v>
@@ -14517,7 +14518,7 @@
         <v>0.6320588540047658</v>
       </c>
       <c r="BV40" s="0">
-        <v>1.0483210483210474</v>
+        <v>1.0483210483210475</v>
       </c>
       <c r="BW40" s="0">
         <v>0.70175438596491169</v>
@@ -14526,7 +14527,7 @@
         <v>0.61702426027205104</v>
       </c>
       <c r="BY40" s="0">
-        <v>1.282051282051281</v>
+        <v>1.2820512820512811</v>
       </c>
       <c r="BZ40" s="0">
         <v>0.80305423907319573</v>
@@ -14672,7 +14673,7 @@
         <v>0.75950058738354709</v>
       </c>
       <c r="E41" s="0">
-        <v>0.66348939351462421</v>
+        <v>0.66348939351462422</v>
       </c>
       <c r="F41" s="0">
         <v>0.80915899113368273</v>
@@ -14684,7 +14685,7 @@
         <v>0.62569381370471233</v>
       </c>
       <c r="I41" s="0">
-        <v>0.94684385382059721</v>
+        <v>0.94684385382059722</v>
       </c>
       <c r="J41" s="0">
         <v>0.79288957094443313</v>
@@ -14732,7 +14733,7 @@
         <v>0.64430547659655057</v>
       </c>
       <c r="Y41" s="0">
-        <v>0.68134171907756746</v>
+        <v>0.68134171907756747</v>
       </c>
       <c r="Z41" s="0">
         <v>0.98375657744223199</v>
@@ -14837,7 +14838,7 @@
         <v>1.361675908810843</v>
       </c>
       <c r="BH41" s="0">
-        <v>1.4558232931726895</v>
+        <v>1.4558232931726896</v>
       </c>
       <c r="BI41" s="0">
         <v>0.76743769051461297</v>
@@ -14894,7 +14895,7 @@
         <v>0.68457082675092096</v>
       </c>
       <c r="CA41" s="0">
-        <v>0.25062656641603986</v>
+        <v>0.25062656641603987</v>
       </c>
       <c r="CB41" s="0">
         <v>0.4199475065616794</v>
@@ -14966,7 +14967,7 @@
         <v>3.1479705976350241</v>
       </c>
       <c r="CY41" s="0">
-        <v>0.24313153415998034</v>
+        <v>0.24313153415998035</v>
       </c>
       <c r="CZ41" s="0">
         <v>0.13982754602656711</v>
@@ -15049,7 +15050,7 @@
         <v>0.88039867109634473</v>
       </c>
       <c r="J42" s="0">
-        <v>0.53072447087409635</v>
+        <v>0.53072447087409636</v>
       </c>
       <c r="K42" s="0">
         <v>0.76016723679209364</v>
@@ -15064,7 +15065,7 @@
         <v>0.3426791277258564</v>
       </c>
       <c r="O42" s="0">
-        <v>0.55368795728692854</v>
+        <v>0.55368795728692855</v>
       </c>
       <c r="P42" s="0">
         <v>0.53460729113348071</v>
@@ -15193,7 +15194,7 @@
         <v>1.1876855758712288</v>
       </c>
       <c r="BF42" s="0">
-        <v>0.2637789809801469</v>
+        <v>0.26377898098014691</v>
       </c>
       <c r="BG42" s="0">
         <v>1.3924830560690067</v>
@@ -15232,7 +15233,7 @@
         <v>0.25026237184144645</v>
       </c>
       <c r="BS42" s="0">
-        <v>1.0783957348842836</v>
+        <v>1.0783957348842837</v>
       </c>
       <c r="BT42" s="0">
         <v>0.57237344187229666</v>
@@ -15471,7 +15472,7 @@
         <v>0.023640661938534261</v>
       </c>
       <c r="AD43" s="0">
-        <v>1.4513442778967391</v>
+        <v>1.4513442778967392</v>
       </c>
       <c r="AE43" s="0">
         <v>0.47814207650273183</v>
@@ -15507,13 +15508,13 @@
         <v>0.10486891385767781</v>
       </c>
       <c r="AP43" s="0">
-        <v>0.8682855040470927</v>
+        <v>0.86828550404709271</v>
       </c>
       <c r="AQ43" s="0">
         <v>0.52932761087267477</v>
       </c>
       <c r="AR43" s="0">
-        <v>1.3084112149532698</v>
+        <v>1.3084112149532699</v>
       </c>
       <c r="AS43" s="0">
         <v>1.0582010582010573</v>
@@ -15708,7 +15709,7 @@
         <v>0.042501517911353939</v>
       </c>
       <c r="DE43" s="0">
-        <v>0.19333011116481374</v>
+        <v>0.19333011116481375</v>
       </c>
       <c r="DF43" s="0">
         <v>0</v>
@@ -15732,7 +15733,7 @@
         <v>0.043516100957354184</v>
       </c>
       <c r="DM43" s="0">
-        <v>0.64102564102564052</v>
+        <v>0.64102564102564053</v>
       </c>
       <c r="DN43" s="0">
         <v>0</v>
@@ -15788,7 +15789,7 @@
         <v>0.4257528556593973</v>
       </c>
       <c r="O44" s="0">
-        <v>0.3559422582558826</v>
+        <v>0.35594225825588261</v>
       </c>
       <c r="P44" s="0">
         <v>0.34692600807598217</v>
@@ -15842,7 +15843,7 @@
         <v>0.63157894736842057</v>
       </c>
       <c r="AG44" s="0">
-        <v>1.1468236004225127</v>
+        <v>1.1468236004225128</v>
       </c>
       <c r="AH44" s="0">
         <v>0.72946400253726551</v>
@@ -15908,7 +15909,7 @@
         <v>0.89690518430908661</v>
       </c>
       <c r="BC44" s="0">
-        <v>1.1723379041814785</v>
+        <v>1.1723379041814786</v>
       </c>
       <c r="BD44" s="0">
         <v>0.62350119904076684</v>
@@ -15935,7 +15936,7 @@
         <v>0.70746617212720597</v>
       </c>
       <c r="BL44" s="0">
-        <v>0.44580308240988364</v>
+        <v>0.44580308240988365</v>
       </c>
       <c r="BM44" s="0">
         <v>1.1298452981053353</v>
@@ -15965,7 +15966,7 @@
         <v>0.29012537560874496</v>
       </c>
       <c r="BV44" s="0">
-        <v>0.76986076986076923</v>
+        <v>0.76986076986076924</v>
       </c>
       <c r="BW44" s="0">
         <v>0.55555555555555503</v>
@@ -16064,7 +16065,7 @@
         <v>0.026123301985370925</v>
       </c>
       <c r="DC44" s="0">
-        <v>0.46400239485106975</v>
+        <v>0.46400239485106976</v>
       </c>
       <c r="DD44" s="0">
         <v>0.018214936247723117</v>
@@ -16135,7 +16136,7 @@
         <v>0.44850498338870387</v>
       </c>
       <c r="J45" s="0">
-        <v>0.38365624400537079</v>
+        <v>0.3836562440053708</v>
       </c>
       <c r="K45" s="0">
         <v>0.55112124667426776</v>
@@ -16273,7 +16274,7 @@
         <v>1.185034704587776</v>
       </c>
       <c r="BD45" s="0">
-        <v>0.4248030147310719</v>
+        <v>0.42480301473107191</v>
       </c>
       <c r="BE45" s="0">
         <v>0.7813720893889663</v>
@@ -16482,7 +16483,7 @@
         <v>0.39341037619867475</v>
       </c>
       <c r="E46" s="0">
-        <v>0.28346260474099177</v>
+        <v>0.28346260474099178</v>
       </c>
       <c r="F46" s="0">
         <v>0.35293104932426844</v>
@@ -16503,13 +16504,13 @@
         <v>0.38008361839604959</v>
       </c>
       <c r="L46" s="0">
-        <v>0.4262120404901466</v>
+        <v>0.42621204049014661</v>
       </c>
       <c r="M46" s="0">
         <v>0.24948024948025113</v>
       </c>
       <c r="N46" s="0">
-        <v>0.29075804776739544</v>
+        <v>0.29075804776739545</v>
       </c>
       <c r="O46" s="0">
         <v>0.21752026893415211</v>
@@ -16635,7 +16636,7 @@
         <v>1.0961571017437011</v>
       </c>
       <c r="BD46" s="0">
-        <v>0.48646796848236012</v>
+        <v>0.48646796848236013</v>
       </c>
       <c r="BE46" s="0">
         <v>0.60947022972339826</v>
@@ -16662,7 +16663,7 @@
         <v>0.4203286205578935</v>
       </c>
       <c r="BM46" s="0">
-        <v>0.85172953241787452</v>
+        <v>0.85172953241787453</v>
       </c>
       <c r="BN46" s="0">
         <v>0.80720273207079074</v>
@@ -16773,7 +16774,7 @@
         <v>0</v>
       </c>
       <c r="CX46" s="0">
-        <v>0.25567273889421704</v>
+        <v>0.25567273889421705</v>
       </c>
       <c r="CY46" s="0">
         <v>0.008104384471999404</v>
@@ -16844,7 +16845,7 @@
         <v>0.31964593066142089</v>
       </c>
       <c r="E47" s="0">
-        <v>0.19001339438681727</v>
+        <v>0.19001339438681728</v>
       </c>
       <c r="F47" s="0">
         <v>0.32136810995380305</v>
@@ -16937,7 +16938,7 @@
         <v>0.36485253876558194</v>
       </c>
       <c r="AJ47" s="0">
-        <v>0.25799793601651166</v>
+        <v>0.25799793601651167</v>
       </c>
       <c r="AK47" s="0">
         <v>0.14114850308298033</v>
@@ -16976,10 +16977,10 @@
         <v>1.19979134063641</v>
       </c>
       <c r="AW47" s="0">
-        <v>0.60100466451381362</v>
+        <v>0.60100466451381363</v>
       </c>
       <c r="AX47" s="0">
-        <v>0.76977615719639358</v>
+        <v>0.76977615719639359</v>
       </c>
       <c r="AY47" s="0">
         <v>0.10785305021907642</v>
@@ -17072,7 +17073,7 @@
         <v>0</v>
       </c>
       <c r="CC47" s="0">
-        <v>0.074990626171728469</v>
+        <v>0.07499062617172847</v>
       </c>
       <c r="CD47" s="0">
         <v>0.3846153846153843</v>
@@ -17239,7 +17240,7 @@
         <v>0.17137960582690642</v>
       </c>
       <c r="P48" s="0">
-        <v>0.14218279019507465</v>
+        <v>0.14218279019507466</v>
       </c>
       <c r="Q48" s="0">
         <v>0.36008230452674861</v>
@@ -17335,7 +17336,7 @@
         <v>0.3771018793273983</v>
       </c>
       <c r="AV48" s="0">
-        <v>0.96132349653476334</v>
+        <v>0.96132349653476335</v>
       </c>
       <c r="AW48" s="0">
         <v>0.37674919268030105</v>
@@ -17347,13 +17348,13 @@
         <v>0.12133468149646096</v>
       </c>
       <c r="AZ48" s="0">
-        <v>0.20377917747313803</v>
+        <v>0.20377917747313804</v>
       </c>
       <c r="BA48" s="0">
         <v>0.16776764181608456</v>
       </c>
       <c r="BB48" s="0">
-        <v>0.43366844076483307</v>
+        <v>0.43366844076483308</v>
       </c>
       <c r="BC48" s="0">
         <v>0.91416962925342737</v>
@@ -17431,7 +17432,7 @@
         <v>0</v>
       </c>
       <c r="CB48" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC48" s="0">
         <v>0.049993750781152313</v>
@@ -17601,7 +17602,7 @@
         <v>0.092281326214488091</v>
       </c>
       <c r="P49" s="0">
-        <v>0.14218279019507465</v>
+        <v>0.14218279019507466</v>
       </c>
       <c r="Q49" s="0">
         <v>0.1028806584362139</v>
@@ -17697,7 +17698,7 @@
         <v>0.22873392680514323</v>
       </c>
       <c r="AV49" s="0">
-        <v>0.96132349653476334</v>
+        <v>0.96132349653476335</v>
       </c>
       <c r="AW49" s="0">
         <v>0.34086831718693905</v>
@@ -17763,7 +17764,7 @@
         <v>0.11964584828906426</v>
       </c>
       <c r="BR49" s="0">
-        <v>0.024218939210462562</v>
+        <v>0.024218939210462563</v>
       </c>
       <c r="BS49" s="0">
         <v>0.51294478775394758</v>
@@ -18155,7 +18156,7 @@
         <v>0</v>
       </c>
       <c r="CB50" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC50" s="0">
         <v>0.037495313085864235</v>
@@ -18173,7 +18174,7 @@
         <v>0.36636530166046177</v>
       </c>
       <c r="CH50" s="0">
-        <v>0.33567421933660146</v>
+        <v>0.33567421933660147</v>
       </c>
       <c r="CI50" s="0">
         <v>0.17748197448696601</v>
@@ -18191,7 +18192,7 @@
         <v>0.074529532327184581</v>
       </c>
       <c r="CN50" s="0">
-        <v>0.40679588418281853</v>
+        <v>0.40679588418281854</v>
       </c>
       <c r="CO50" s="0">
         <v>0.54659261218372512</v>
@@ -18316,13 +18317,13 @@
         <v>0.05327650506126793</v>
       </c>
       <c r="M51" s="0">
-        <v>0.027720027720027698</v>
+        <v>0.027720027720027699</v>
       </c>
       <c r="N51" s="0">
         <v>0.093457943925233558</v>
       </c>
       <c r="O51" s="0">
-        <v>0.098872849515522956</v>
+        <v>0.098872849515522957</v>
       </c>
       <c r="P51" s="0">
         <v>0.09668429733265077</v>
@@ -18663,13 +18664,13 @@
         <v>0.080128205128205066</v>
       </c>
       <c r="H52" s="0">
-        <v>0.050459178524573572</v>
+        <v>0.050459178524573573</v>
       </c>
       <c r="I52" s="0">
         <v>0.07751937984496117</v>
       </c>
       <c r="J52" s="0">
-        <v>0.070336978067651323</v>
+        <v>0.070336978067651324</v>
       </c>
       <c r="K52" s="0">
         <v>0.13302926643861637</v>
@@ -18771,7 +18772,7 @@
         <v>0.1144492131616594</v>
       </c>
       <c r="AR52" s="0">
-        <v>0.41121495327102769</v>
+        <v>0.4112149532710277</v>
       </c>
       <c r="AS52" s="0">
         <v>0.066137566137566078</v>
@@ -18783,7 +18784,7 @@
         <v>0.098911968348170051</v>
       </c>
       <c r="AV52" s="0">
-        <v>0.78247261345852825</v>
+        <v>0.78247261345852826</v>
       </c>
       <c r="AW52" s="0">
         <v>0.17940437746681004</v>
@@ -18849,7 +18850,7 @@
         <v>0.047858339315625706</v>
       </c>
       <c r="BR52" s="0">
-        <v>0.024218939210462562</v>
+        <v>0.024218939210462563</v>
       </c>
       <c r="BS52" s="0">
         <v>0.31503695625833</v>
@@ -18879,10 +18880,10 @@
         <v>0.10025062656641595</v>
       </c>
       <c r="CB52" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC52" s="0">
-        <v>0.024996875390576156</v>
+        <v>0.024996875390576157</v>
       </c>
       <c r="CD52" s="0">
         <v>0.23076923076923056</v>
@@ -19019,7 +19020,7 @@
         <v>0.059184499890975871</v>
       </c>
       <c r="F53" s="0">
-        <v>0.068864594990100655</v>
+        <v>0.068864594990100656</v>
       </c>
       <c r="G53" s="0">
         <v>0.10683760683760674</v>
@@ -19043,7 +19044,7 @@
         <v>0.013860013860013849</v>
       </c>
       <c r="N53" s="0">
-        <v>0.041536863966770476</v>
+        <v>0.041536863966770477</v>
       </c>
       <c r="O53" s="0">
         <v>0.046140663107244045</v>
@@ -19085,7 +19086,7 @@
         <v>0.058633831720902911</v>
       </c>
       <c r="AB53" s="0">
-        <v>0.20437359493153467</v>
+        <v>0.20437359493153468</v>
       </c>
       <c r="AC53" s="0">
         <v>0</v>
@@ -19103,7 +19104,7 @@
         <v>0.40742417383431379</v>
       </c>
       <c r="AH53" s="0">
-        <v>0.15065017443704395</v>
+        <v>0.15065017443704396</v>
       </c>
       <c r="AI53" s="0">
         <v>0.050673963717441928</v>
@@ -19121,7 +19122,7 @@
         <v>0.030892801977139301</v>
       </c>
       <c r="AN53" s="0">
-        <v>0.21729682746631881</v>
+        <v>0.21729682746631882</v>
       </c>
       <c r="AO53" s="0">
         <v>0</v>
@@ -19259,7 +19260,7 @@
         <v>0.18318265083023089</v>
       </c>
       <c r="CH53" s="0">
-        <v>0.18550417384391132</v>
+        <v>0.18550417384391133</v>
       </c>
       <c r="CI53" s="0">
         <v>0.088740987243483005</v>
@@ -19283,7 +19284,7 @@
         <v>0.28211231596579367</v>
       </c>
       <c r="CP53" s="0">
-        <v>0.38373905744093983</v>
+        <v>0.38373905744093984</v>
       </c>
       <c r="CQ53" s="0">
         <v>0</v>
@@ -19387,7 +19388,7 @@
         <v>0.066773504273504203</v>
       </c>
       <c r="H54" s="0">
-        <v>0.050459178524573572</v>
+        <v>0.050459178524573573</v>
       </c>
       <c r="I54" s="0">
         <v>0.083056478405315534</v>
@@ -19420,7 +19421,7 @@
         <v>0.091827364554637206</v>
       </c>
       <c r="S54" s="0">
-        <v>0.046438190768087632</v>
+        <v>0.046438190768087633</v>
       </c>
       <c r="T54" s="0">
         <v>0.027316806665300803</v>
@@ -19504,13 +19505,13 @@
         <v>0.33388981636060072</v>
       </c>
       <c r="AU54" s="0">
-        <v>0.037091988130563767</v>
+        <v>0.037091988130563768</v>
       </c>
       <c r="AV54" s="0">
         <v>0.46948356807511699</v>
       </c>
       <c r="AW54" s="0">
-        <v>0.14352350197344801</v>
+        <v>0.14352350197344802</v>
       </c>
       <c r="AX54" s="0">
         <v>0.16205813835713548</v>
@@ -19525,7 +19526,7 @@
         <v>0.02097095522701057</v>
       </c>
       <c r="BB54" s="0">
-        <v>0.23654642223536348</v>
+        <v>0.23654642223536349</v>
       </c>
       <c r="BC54" s="0">
         <v>0.28779414254274566</v>
@@ -19645,7 +19646,7 @@
         <v>0.21158423697434522</v>
       </c>
       <c r="CP54" s="0">
-        <v>0.38373905744093983</v>
+        <v>0.38373905744093984</v>
       </c>
       <c r="CQ54" s="0">
         <v>0</v>
@@ -19755,7 +19756,7 @@
         <v>0.044296788482835282</v>
       </c>
       <c r="J55" s="0">
-        <v>0.04475989513396026</v>
+        <v>0.044759895133960261</v>
       </c>
       <c r="K55" s="0">
         <v>0.038008361839604959</v>
@@ -19863,10 +19864,10 @@
         <v>0.066137566137566564</v>
       </c>
       <c r="AT55" s="0">
-        <v>0.22259321090706879</v>
+        <v>0.2225932109070688</v>
       </c>
       <c r="AU55" s="0">
-        <v>0.068001978239367405</v>
+        <v>0.068001978239367406</v>
       </c>
       <c r="AV55" s="0">
         <v>0.4620314479469439</v>
@@ -20156,7 +20157,7 @@
         <v>0</v>
       </c>
       <c r="W56" s="0">
-        <v>0.085470085470085388</v>
+        <v>0.085470085470085389</v>
       </c>
       <c r="X56" s="0">
         <v>0</v>
@@ -20270,7 +20271,7 @@
         <v>0.34024988844265924</v>
       </c>
       <c r="BI56" s="0">
-        <v>0.032275416890801475</v>
+        <v>0.032275416890801476</v>
       </c>
       <c r="BJ56" s="0">
         <v>0.092131932927952742</v>
@@ -20297,7 +20298,7 @@
         <v>0.011964584828906426</v>
       </c>
       <c r="BR56" s="0">
-        <v>0.024218939210462562</v>
+        <v>0.024218939210462563</v>
       </c>
       <c r="BS56" s="0">
         <v>0.13732380144593873</v>
@@ -20728,7 +20729,7 @@
         <v>0.11964584828906426</v>
       </c>
       <c r="CO57" s="0">
-        <v>0.13224014810896575</v>
+        <v>0.13224014810896576</v>
       </c>
       <c r="CP57" s="0">
         <v>0.20386137426549927</v>
@@ -20979,7 +20980,7 @@
         <v>0.13966480446927362</v>
       </c>
       <c r="BD58" s="0">
-        <v>0.054813292223364118</v>
+        <v>0.054813292223364119</v>
       </c>
       <c r="BE58" s="0">
         <v>0.015627441787779327</v>
@@ -21006,7 +21007,7 @@
         <v>0.0063686154629983387</v>
       </c>
       <c r="BM58" s="0">
-        <v>0.092705255229155722</v>
+        <v>0.092705255229155723</v>
       </c>
       <c r="BN58" s="0">
         <v>0.062092517851598833</v>
@@ -21093,7 +21094,7 @@
         <v>0.12783214317200026</v>
       </c>
       <c r="CP58" s="0">
-        <v>0.13191030099532305</v>
+        <v>0.13191030099532306</v>
       </c>
       <c r="CQ58" s="0">
         <v>0</v>
@@ -21341,7 +21342,7 @@
         <v>0.16082613847976962</v>
       </c>
       <c r="BD59" s="0">
-        <v>0.020554984583761544</v>
+        <v>0.020554984583761545</v>
       </c>
       <c r="BE59" s="0">
         <v>0.04688232536333798</v>
@@ -21377,7 +21378,7 @@
         <v>0</v>
       </c>
       <c r="BP59" s="0">
-        <v>0.02204585537918869</v>
+        <v>0.022045855379188691</v>
       </c>
       <c r="BQ59" s="0">
         <v>0.011964584828906426</v>
@@ -21389,7 +21390,7 @@
         <v>0.056545094713033595</v>
       </c>
       <c r="BT59" s="0">
-        <v>0.0084796065462562457</v>
+        <v>0.0084796065462562458</v>
       </c>
       <c r="BU59" s="0">
         <v>0.010361620557455176</v>
@@ -21730,7 +21731,7 @@
         <v>0.0063686154629983387</v>
       </c>
       <c r="BM60" s="0">
-        <v>0.092705255229155722</v>
+        <v>0.092705255229155723</v>
       </c>
       <c r="BN60" s="0">
         <v>0.051743764876332358</v>
@@ -22669,7 +22670,7 @@
         <v>0</v>
       </c>
       <c r="P63" s="0">
-        <v>0.0056873116078030288</v>
+        <v>0.0056873116078030289</v>
       </c>
       <c r="Q63" s="0">
         <v>0</v>
@@ -22711,7 +22712,7 @@
         <v>0</v>
       </c>
       <c r="AD63" s="0">
-        <v>0.023792529145848357</v>
+        <v>0.023792529145848358</v>
       </c>
       <c r="AE63" s="0">
         <v>0</v>
@@ -24264,7 +24265,7 @@
         <v>0</v>
       </c>
       <c r="BM67" s="0">
-        <v>0.017382235355466825</v>
+        <v>0.017382235355466826</v>
       </c>
       <c r="BN67" s="0">
         <v>0.010348752975266547</v>

--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_pet/sub-0004_ses-01_pet_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_pet/sub-0004_ses-01_pet_pdf.xlsx
@@ -1,7 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
